--- a/output/pdf_financials_xlsx/VDO.H.xlsx
+++ b/output/pdf_financials_xlsx/VDO.H.xlsx
@@ -5402,7 +5402,7 @@
         <v>3.620847</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.43645</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -6697,22 +6697,22 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.623755</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-6.739694</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.303865</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.59115</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>1.626722</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>5.692497</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -9500,7 +9500,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10758,7 +10762,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -23666,7 +23674,11 @@
           <t>Impairment of mining properties and deferred exploration and evaluation expenditures 6, 7</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -24390,7 +24402,11 @@
           <t>Impairment of mining properties and deferred exploration and evaluation expenditures 5, 6</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -24657,7 +24673,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
         <v>-1.623755</v>
       </c>
@@ -25444,7 +25464,11 @@
           <t>Impairment of mining properties and deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VDO.H.xlsx
+++ b/output/pdf_financials_xlsx/VDO.H.xlsx
@@ -985,16 +985,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004324</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.042468</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.015608</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006501</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.484801</v>
+        <v>-0.489125</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.997812</v>
+        <v>-2.04028</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.24416</v>
+        <v>-3.259768</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.337672</v>
+        <v>-1.344173</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.103739</v>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.484501</v>
+        <v>-0.488825</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.996811</v>
+        <v>-2.039279</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.242636</v>
+        <v>-3.258244</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.336148</v>
+        <v>-1.342649</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.102215</v>
@@ -2276,13 +2276,13 @@
         <v>0.006781</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.004656</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.038319</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.8052009999999999</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.773155</v>
@@ -2380,13 +2380,13 @@
         <v>0.006781</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.004656</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.038319</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.145873</v>
+        <v>0.951074</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.773155</v>
@@ -3004,13 +3004,13 @@
         <v>0.005137</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009221999999999999</v>
+        <v>0.004566</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.04408</v>
+        <v>0.005761</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.8121119999999999</v>
+        <v>0.006911</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.001145</v>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -37862,7 +37862,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -38841,7 +38841,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E350" s="5" t="n">

--- a/output/pdf_financials_xlsx/VDO.H.xlsx
+++ b/output/pdf_financials_xlsx/VDO.H.xlsx
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.17663</v>
+        <v>0.17663</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.185667</v>
@@ -6571,16 +6571,16 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.414107</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.128593</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -17611,7 +17611,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -18861,7 +18865,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -19134,7 +19142,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -24495,7 +24507,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -25555,7 +25571,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -26451,7 +26471,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -37680,7 +37704,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -37951,7 +37979,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -38570,7 +38602,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -38932,7 +38968,11 @@
           <t>Deferred income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E351" s="5" t="n">
         <v>-0.17663</v>
       </c>
